--- a/healthcare_forms/016_injectable_application_knowledge_quiz--healthcare_forms.xlsx
+++ b/healthcare_forms/016_injectable_application_knowledge_quiz--healthcare_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="29" customWidth="1" min="2" max="2"/>
-    <col width="29" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -525,7 +525,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>introduction</t>
+          <t>What is the purpose of this quiz?</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -548,7 +548,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>injectable_medications</t>
+          <t>List all injectable medications used in your practice</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -571,7 +571,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>correct_injection_technique</t>
+          <t>What is the correct injection technique for each medication?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -594,7 +594,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>patient_consent</t>
+          <t>What is the patient consent process?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -617,7 +617,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>injection_site</t>
+          <t>What is the injection site?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -640,7 +640,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>allergies</t>
+          <t>List all patient allergies</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -663,7 +663,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>medical_conditions</t>
+          <t>List all patient medical conditions</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -686,7 +686,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>safety_precautions</t>
+          <t>What are the safety precautions to take?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -709,7 +709,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>emergency_procedures</t>
+          <t>What are the emergency procedures to follow?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -732,7 +732,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>post_injection</t>
+          <t>What post-injection instructions are given to the patient?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -750,12 +750,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>additional_comments</t>
+          <t>final_questions</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>additional_comments</t>
+          <t>Is there anything else you'd like to add?</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -768,17 +768,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>assessment</t>
+          <t>submit</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>assessment</t>
+          <t>Submit your answers</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -796,12 +796,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>assessment</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>Assessment</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -814,17 +814,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>final_questions</t>
+          <t>review</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>final_questions</t>
+          <t>Is there anything you'd like to review before submission?</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -837,17 +837,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>submit</t>
+          <t>submission</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>submit</t>
+          <t>Submission</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -860,17 +860,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>16_final_questions</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>Do you have any additional comments?</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -883,17 +883,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>additional_comments</t>
+          <t>17_submit_answers</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>additional_comments</t>
+          <t>Please type 'submit' to finish the survey</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -906,182 +906,21 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>final_questions</t>
+          <t>18_review</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>final_questions</t>
+          <t>Please review your answers before submitting</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>submit</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>submit</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>submission</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>submission</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>review</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>review</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>review</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>review</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>final_questions</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>final_questions</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>review</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>review</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>submission</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>submission</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1098,12 +937,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C34"/>
+  <dimension ref="A1:C20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="37" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +970,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>anaphylaxis</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Anaphylaxis</t>
         </is>
       </c>
     </row>
@@ -1148,12 +987,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>pain_relief</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Pain relief</t>
         </is>
       </c>
     </row>
@@ -1165,29 +1004,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>sedation</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Sedation</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>correct_injection_technique_choices</t>
+          <t>injectable_medications_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>antibiotics</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Antibiotics</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1038,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>subcutaneous</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Subcutaneous</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1055,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>intramuscular</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Intramuscular</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1072,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>warning_signs</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Warning signs</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1089,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>dosage</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Dosage</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1106,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>side_effects</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Side effects</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1123,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>cpr</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>CPR</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1140,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>tourniquet</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Tourniquet</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1157,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>anaphylaxis_protocol</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Anaphylaxis protocol</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1174,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>pass</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -1352,335 +1191,97 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>fail</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Fail</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>assessment_choices</t>
+          <t>submission_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>review_choices</t>
+          <t>submission_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>review_choices</t>
+          <t>16_final_questions_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>review_choices</t>
+          <t>16_final_questions_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>final_questions_choices</t>
+          <t>16_final_questions_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>other_(please_specify)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>option1</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>final_questions_choices</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>option2</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>option2</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>final_questions_choices</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>option3</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>option3</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>final_questions_choices</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>option1</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>option1</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>final_questions_choices</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>option2</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>option2</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>final_questions_choices</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>option3</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>option3</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>submission_choices</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>option1</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>option1</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>submission_choices</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>option2</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>option2</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>submission_choices</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>option3</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>option3</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>final_questions_choices</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>option1</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>option1</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>final_questions_choices</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>option2</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>option2</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>final_questions_choices</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>option3</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>option3</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>submission_choices</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>option1</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>option1</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>submission_choices</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>option2</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>option2</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>submission_choices</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>option3</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>option3</t>
+          <t>Other (please specify)</t>
         </is>
       </c>
     </row>
